--- a/Excel/Common_v02.xlsx
+++ b/Excel/Common_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97636EF-EAD0-493E-AE53-0B708F465711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9154B3-3CE5-4AE1-8EED-CCC3765E414D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="255" windowWidth="37755" windowHeight="20445" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="570" yWindow="345" windowWidth="37755" windowHeight="20445" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="3" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
+    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
@@ -40,6 +41,7 @@
     <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
     <definedName name="Common_InputFunctions.Utility_GetClimateZone">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
@@ -100,6 +102,12 @@
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4: Chapter 11: N2O Emissions from Managed Soils, and CO2 Emissions from Lime and Urea Application")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Source">_xlfn.LAMBDA("VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Title">_xlfn.LAMBDA("FracWET for irrigation types")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Unit">_xlfn.LAMBDA("dimensionless")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
@@ -230,7 +238,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>Climate zone</t>
   </si>
@@ -368,6 +376,9 @@
   </si>
   <si>
     <t>Acknowledgements</t>
+  </si>
+  <si>
+    <t>Irrigation type i</t>
   </si>
 </sst>
 </file>
@@ -894,7 +905,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -929,6 +940,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="54">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,7 +1007,31 @@
     <cellStyle name="Unit no indent" xfId="53" xr:uid="{2829D020-DAD8-4B7D-9262-450720E27D2B}"/>
     <cellStyle name="Unit total" xfId="25" xr:uid="{65428923-3DAD-47B6-8DDF-0EBD05E7C55B}"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1604,20 +1642,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="28"/>
-      <tableStyleElement type="headerRow" dxfId="27"/>
-      <tableStyleElement type="totalRow" dxfId="26"/>
-      <tableStyleElement type="firstColumn" dxfId="25"/>
-      <tableStyleElement type="firstRowStripe" dxfId="24"/>
-      <tableStyleElement type="secondRowStripe" dxfId="23"/>
+      <tableStyleElement type="wholeTable" dxfId="29"/>
+      <tableStyleElement type="headerRow" dxfId="28"/>
+      <tableStyleElement type="totalRow" dxfId="27"/>
+      <tableStyleElement type="firstColumn" dxfId="26"/>
+      <tableStyleElement type="firstRowStripe" dxfId="25"/>
+      <tableStyleElement type="secondRowStripe" dxfId="24"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="22"/>
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstColumn" dxfId="19"/>
-      <tableStyleElement type="firstRowStripe" dxfId="18"/>
-      <tableStyleElement type="secondRowStripe" dxfId="17"/>
+      <tableStyleElement type="wholeTable" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="totalRow" dxfId="21"/>
+      <tableStyleElement type="firstColumn" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -1733,8 +1771,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1BFC15E8-D67C-4277-8EF9-438444043863}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D142:E147" totalsRowShown="0">
-  <autoFilter ref="D142:E147" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1BFC15E8-D67C-4277-8EF9-438444043863}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+  <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
@@ -1760,7 +1798,7 @@
     <tableColumn id="1" xr3:uid="{CA74DB79-CAE7-4EF8-BA48-96421E9E9373}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1769,8 +1807,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{CFF24A4D-FB3A-4990-A60E-B22F27A25574}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D175:H188" totalsRowShown="0">
-  <autoFilter ref="D175:H188" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{CFF24A4D-FB3A-4990-A60E-B22F27A25574}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+  <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1792,6 +1830,24 @@
     </tableColumn>
     <tableColumn id="5" xr3:uid="{3490D434-A455-4128-8D9F-A4C3B5BCB722}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+  <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{B18D772B-2FE9-457A-A200-8E17C55C340C}" name="Irrigation type i">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1884,49 +1940,49 @@
     <tableColumn id="1" xr3:uid="{8938BBE8-7B92-48A9-872B-3320D21DB635}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="16" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="17" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="15" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="16" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="14" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="15" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="13" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="14" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="12" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="13" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="11" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="12" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="10" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="11" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="9" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="10" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="8" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="9" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="7" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="8" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="6" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="7" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="5" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="6" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="4" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="5" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="3" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="4" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="2" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="3" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1944,7 +2000,7 @@
     <tableColumn id="1" xr3:uid="{2FCD4A06-823B-4A3F-89D0-46C27A9E1AA9}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="1" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="2" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2245,7 +2301,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="1032" row="3">
+  <wetp:taskpane dockstate="right" visibility="0" width="984" row="3">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2292,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83968956-F921-4291-AAEE-DE11952DD430}">
-  <dimension ref="A1:BX196"/>
+  <dimension ref="A1:BX199"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
@@ -3975,8 +4031,8 @@
     </row>
     <row r="139" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="5" t="str" cm="1">
-        <f t="array" ref="D139">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
-        <v>Australian data scores for scope 3</v>
+        <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
+        <v>FracWET for irrigation types</v>
       </c>
       <c r="BM139" s="6"/>
       <c r="BN139" s="6"/>
@@ -3993,8 +4049,8 @@
     </row>
     <row r="140" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D140" s="4" t="str" cm="1">
-        <f t="array" ref="D140">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
-        <v>VEERG 2026: XXXXXXXX</v>
+        <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
+        <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
       </c>
       <c r="BM140" s="6"/>
       <c r="BN140" s="6"/>
@@ -4010,69 +4066,73 @@
       <c r="BX140" s="6"/>
     </row>
     <row r="141" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D141" s="13" t="str" cm="1">
+        <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
+        <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
+      </c>
       <c r="BM141" s="6"/>
     </row>
     <row r="142" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D142" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E142" s="11" t="s">
-        <v>35</v>
+      <c r="D142" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E142" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="BM142" s="6"/>
     </row>
     <row r="143" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D143" s="11" t="str" cm="1">
-        <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>International scope 3 database</v>
-      </c>
-      <c r="E143" s="11" cm="1">
-        <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+      <c r="D143" s="14" t="str" cm="1">
+        <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="E143" s="14" cm="1">
+        <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM143" s="6"/>
+    </row>
+    <row r="144" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D144" s="1" t="str" cm="1">
+        <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Drip irrigation</v>
+      </c>
+      <c r="E144" s="11" cm="1">
+        <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM144" s="6"/>
+    </row>
+    <row r="145" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D145" s="1" t="str" cm="1">
+        <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Sprinkler irrigation</v>
+      </c>
+      <c r="E145" s="11" cm="1">
+        <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BM143" s="6"/>
-    </row>
-    <row r="144" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D144" s="11" t="str" cm="1">
-        <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Australian scope 3 database</v>
-      </c>
-      <c r="E144" s="11" cm="1">
-        <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>2</v>
-      </c>
-      <c r="BM144" s="6"/>
-    </row>
-    <row r="145" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D145" s="11" t="str" cm="1">
-        <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>State or regional scope 3 database</v>
-      </c>
-      <c r="E145" s="11" cm="1">
-        <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>3</v>
-      </c>
       <c r="BM145" s="6"/>
     </row>
     <row r="146" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D146" s="11" t="str" cm="1">
-        <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Emissions intensity calculated from approved method</v>
+      <c r="D146" s="1" t="str" cm="1">
+        <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Surface irrigation</v>
       </c>
       <c r="E146" s="11" cm="1">
-        <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>4</v>
+        <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>1</v>
       </c>
       <c r="BM146" s="6"/>
     </row>
     <row r="147" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D147" s="11" t="str" cm="1">
-        <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Verified credential matching ISO14067</v>
+      <c r="D147" s="1" t="str" cm="1">
+        <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Other irrigation</v>
       </c>
       <c r="E147" s="11" cm="1">
-        <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>5</v>
+        <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>1</v>
       </c>
       <c r="BM147" s="6"/>
     </row>
@@ -4084,35 +4144,27 @@
     </row>
     <row r="150" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="5" t="str" cm="1">
-        <f t="array" ref="D150">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
-        <v>Fraction of N that is available for leaching and runoff</v>
-      </c>
-      <c r="E150" s="10"/>
+        <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
+        <v>Australian data scores for scope 3</v>
+      </c>
       <c r="BM150" s="6"/>
     </row>
     <row r="151" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="4" t="str" cm="1">
-        <f t="array" ref="D151">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
-        <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
-      </c>
-      <c r="E151" s="10"/>
+        <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
+        <v>VEERG 2026: XXXXXXXX</v>
+      </c>
       <c r="BM151" s="6"/>
     </row>
     <row r="152" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D152" s="4" t="str" cm="1">
-        <f t="array" ref="D152">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
-        <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
-      </c>
-      <c r="E152" s="10"/>
       <c r="BM152" s="6"/>
     </row>
     <row r="153" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D153" s="10" t="str" cm="1">
-        <f t="array" ref="D153:E153">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
-        <v>FracLEACH</v>
-      </c>
-      <c r="E153" s="10">
-        <v>0.24</v>
+      <c r="D153" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E153" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="BB153" s="2"/>
       <c r="BC153" s="2"/>
@@ -4127,6 +4179,14 @@
       <c r="BL153" s="2"/>
     </row>
     <row r="154" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D154" s="11" t="str" cm="1">
+        <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>International scope 3 database</v>
+      </c>
+      <c r="E154" s="11" cm="1">
+        <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>1</v>
+      </c>
       <c r="BB154" s="2"/>
       <c r="BC154" s="2"/>
       <c r="BD154" s="2"/>
@@ -4140,6 +4200,14 @@
       <c r="BL154" s="2"/>
     </row>
     <row r="155" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D155" s="11" t="str" cm="1">
+        <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>Australian scope 3 database</v>
+      </c>
+      <c r="E155" s="11" cm="1">
+        <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>2</v>
+      </c>
       <c r="BB155" s="2"/>
       <c r="BC155" s="2"/>
       <c r="BD155" s="2"/>
@@ -4153,54 +4221,65 @@
       <c r="BL155" s="2"/>
     </row>
     <row r="156" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D156" s="5" t="str" cm="1">
-        <f t="array" ref="D156">Common_SourceData.Common_SourceData_EFleach_Title()</f>
-        <v>Emission factor for nitrogen leaching and runoff</v>
+      <c r="D156" s="11" t="str" cm="1">
+        <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>State or regional scope 3 database</v>
+      </c>
+      <c r="E156" s="11" cm="1">
+        <f t="array" ref="E156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D157" s="4" t="str" cm="1">
-        <f t="array" ref="D157">Common_SourceData.Common_SourceData_EFleach_Source()</f>
+      <c r="D157" s="11" t="str" cm="1">
+        <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>Emissions intensity calculated from approved method</v>
+      </c>
+      <c r="E157" s="11" cm="1">
+        <f t="array" ref="E157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D158" s="11" t="str" cm="1">
+        <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>Verified credential matching ISO14067</v>
+      </c>
+      <c r="E158" s="11" cm="1">
+        <f t="array" ref="E158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D161" s="5" t="str" cm="1">
+        <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
+        <v>Fraction of N that is available for leaching and runoff</v>
+      </c>
+      <c r="E161" s="10"/>
+    </row>
+    <row r="162" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D162" s="4" t="str" cm="1">
+        <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
-    </row>
-    <row r="158" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D158" s="4" t="str" cm="1">
-        <f t="array" ref="D158">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
-        <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
-      </c>
-    </row>
-    <row r="159" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D159" s="1" t="str" cm="1">
-        <f t="array" ref="D159:E159">Common_SourceData.Common_SourceData_EFleach_Data()</f>
-        <v>EFleach</v>
-      </c>
-      <c r="E159" s="1">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="160" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D162" s="5" t="str" cm="1">
-        <f t="array" ref="D162">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
-        <v>p = density of methane</v>
-      </c>
+      <c r="E162" s="10"/>
     </row>
     <row r="163" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="4" t="str" cm="1">
-        <f t="array" ref="D163">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
-        <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
-      </c>
+        <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
+        <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
+      </c>
+      <c r="E163" s="10"/>
     </row>
     <row r="164" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D164" s="1" cm="1">
-        <f t="array" ref="D164">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
-        <v>0.6784</v>
-      </c>
-      <c r="E164" s="12" t="str" cm="1">
-        <f t="array" ref="E164">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
-        <v>kg/m3</v>
+      <c r="D164" s="10" t="str" cm="1">
+        <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
+        <v>FracLEACH</v>
+      </c>
+      <c r="E164" s="10">
+        <v>0.24</v>
       </c>
     </row>
     <row r="165" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4215,8 +4294,8 @@
     </row>
     <row r="167" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="5" t="str" cm="1">
-        <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
-        <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
+        <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
+        <v>Emission factor for nitrogen leaching and runoff</v>
       </c>
       <c r="BM167" s="6"/>
       <c r="BN167" s="6"/>
@@ -4224,349 +4303,164 @@
     </row>
     <row r="168" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="4" t="str" cm="1">
-        <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
-        <v>VEERG 2026: Table A.2.2.1</v>
+        <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
+        <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="BM168" s="6"/>
       <c r="BN168" s="6"/>
       <c r="BO168" s="6"/>
     </row>
     <row r="169" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D169" s="12" t="str" cm="1">
-        <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
-        <v>(kg N2O-N / kg N</v>
+      <c r="D169" s="4" t="str" cm="1">
+        <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
+        <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
       </c>
       <c r="BM169" s="6"/>
       <c r="BN169" s="6"/>
       <c r="BO169" s="6"/>
     </row>
     <row r="170" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D170" s="13" t="str" cm="1">
-        <f t="array" ref="D170:D174">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
-        <v>VARIATION OF SOURCE DATA:</v>
+      <c r="D170" s="1" t="str" cm="1">
+        <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
+        <v>EFleach</v>
+      </c>
+      <c r="E170" s="1">
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="BM170" s="6"/>
       <c r="BN170" s="6"/>
       <c r="BO170" s="6"/>
     </row>
     <row r="171" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D171" s="13" t="str">
-        <v>Removed duplicate 'Aquaculture' row.</v>
-      </c>
       <c r="BM171" s="6"/>
       <c r="BN171" s="6"/>
       <c r="BO171" s="6"/>
     </row>
     <row r="172" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D172" s="13" t="str">
-        <v>Removed asterisks to aid lookup.</v>
-      </c>
       <c r="BM172" s="6"/>
       <c r="BN172" s="6"/>
       <c r="BO172" s="6"/>
     </row>
     <row r="173" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D173" s="13" t="str">
-        <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
+      <c r="D173" s="5" t="str" cm="1">
+        <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
+        <v>p = density of methane</v>
       </c>
       <c r="BM173" s="6"/>
       <c r="BN173" s="6"/>
       <c r="BO173" s="6"/>
     </row>
     <row r="174" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D174" s="13" t="str">
-        <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
+      <c r="D174" s="4" t="str" cm="1">
+        <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
+        <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
       </c>
       <c r="BM174" s="6"/>
       <c r="BN174" s="6"/>
       <c r="BO174" s="6"/>
     </row>
     <row r="175" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D175" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E175" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F175" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G175" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H175" s="11" t="s">
-        <v>43</v>
+      <c r="D175" s="1" cm="1">
+        <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
+        <v>0.6784</v>
+      </c>
+      <c r="E175" s="12" t="str" cm="1">
+        <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
+        <v>kg/m3</v>
       </c>
       <c r="BM175" s="6"/>
       <c r="BN175" s="6"/>
       <c r="BO175" s="6"/>
     </row>
     <row r="176" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D176" s="11" t="str" cm="1">
-        <f t="array" ref="D176">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Irrigated pasture</v>
-      </c>
-      <c r="E176" s="11" cm="1">
-        <f t="array" ref="E176">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="F176" s="11" t="str" cm="1">
-        <f t="array" ref="F176">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
-      </c>
-      <c r="G176" s="11" t="str" cm="1">
-        <f t="array" ref="G176">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="H176" s="11" t="str" cm="1">
-        <f t="array" ref="H176">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
-      </c>
       <c r="BM176" s="6"/>
       <c r="BN176" s="6"/>
       <c r="BO176" s="6"/>
     </row>
     <row r="177" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D177" s="11" t="str" cm="1">
-        <f t="array" ref="D177">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Irrigated crop</v>
-      </c>
-      <c r="E177" s="11" cm="1">
-        <f t="array" ref="E177">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="F177" s="11" t="str" cm="1">
-        <f t="array" ref="F177">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
-      </c>
-      <c r="G177" s="11" t="str" cm="1">
-        <f t="array" ref="G177">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="H177" s="11" t="str" cm="1">
-        <f t="array" ref="H177">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
-      </c>
       <c r="BM177" s="6"/>
       <c r="BN177" s="6"/>
       <c r="BO177" s="6"/>
     </row>
     <row r="178" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D178" s="11" t="str" cm="1">
-        <f t="array" ref="D178">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated pasture</v>
-      </c>
-      <c r="E178" s="11" cm="1">
-        <f t="array" ref="E178">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
-      </c>
-      <c r="F178" s="11" t="str" cm="1">
-        <f t="array" ref="F178">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
-      </c>
-      <c r="G178" s="11" t="str" cm="1">
-        <f t="array" ref="G178">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
-      </c>
-      <c r="H178" s="11" t="str" cm="1">
-        <f t="array" ref="H178">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Low rainfall</v>
+      <c r="D178" s="5" t="str" cm="1">
+        <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
+        <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
       </c>
       <c r="BM178" s="6"/>
       <c r="BN178" s="6"/>
       <c r="BO178" s="6"/>
     </row>
     <row r="179" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D179" s="11" t="str" cm="1">
-        <f t="array" ref="D179">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated pasture</v>
-      </c>
-      <c r="E179" s="11" cm="1">
-        <f t="array" ref="E179">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
-      </c>
-      <c r="F179" s="11" t="str" cm="1">
-        <f t="array" ref="F179">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
-      </c>
-      <c r="G179" s="11" t="str" cm="1">
-        <f t="array" ref="G179">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
-      </c>
-      <c r="H179" s="11" t="str" cm="1">
-        <f t="array" ref="H179">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>High rainfall</v>
+      <c r="D179" s="4" t="str" cm="1">
+        <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
+        <v>VEERG 2026: Table A.2.2.1</v>
       </c>
       <c r="BM179" s="6"/>
       <c r="BN179" s="6"/>
       <c r="BO179" s="6"/>
     </row>
     <row r="180" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D180" s="11" t="str" cm="1">
-        <f t="array" ref="D180">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated crop (low rainfall)</v>
-      </c>
-      <c r="E180" s="11" cm="1">
-        <f t="array" ref="E180">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="F180" s="11" t="str" cm="1">
-        <f t="array" ref="F180">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
-      </c>
-      <c r="G180" s="11" t="str" cm="1">
-        <f t="array" ref="G180">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
-      </c>
-      <c r="H180" s="11" t="str" cm="1">
-        <f t="array" ref="H180">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Low rainfall</v>
+      <c r="D180" s="12" t="str" cm="1">
+        <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
+        <v>(kg N2O-N / kg N</v>
       </c>
     </row>
     <row r="181" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D181" s="11" t="str" cm="1">
-        <f t="array" ref="D181">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated crop (high rainfall)</v>
-      </c>
-      <c r="E181" s="11" cm="1">
-        <f t="array" ref="E181">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="F181" s="11" t="str" cm="1">
-        <f t="array" ref="F181">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
-      </c>
-      <c r="G181" s="11" t="str" cm="1">
-        <f t="array" ref="G181">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
-      </c>
-      <c r="H181" s="11" t="str" cm="1">
-        <f t="array" ref="H181">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>High rainfall</v>
+      <c r="D181" s="13" t="str" cm="1">
+        <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
+        <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="182" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D182" s="11" t="str" cm="1">
-        <f t="array" ref="D182">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Sugar</v>
-      </c>
-      <c r="E182" s="11" cm="1">
-        <f t="array" ref="E182">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="F182" s="11" t="str" cm="1">
-        <f t="array" ref="F182">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Sugar</v>
-      </c>
-      <c r="G182" s="11" t="str" cm="1">
-        <f t="array" ref="G182">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="H182" s="11" t="str" cm="1">
-        <f t="array" ref="H182">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+      <c r="D182" s="13" t="str">
+        <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
     <row r="183" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D183" s="11" t="str" cm="1">
-        <f t="array" ref="D183">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Cotton</v>
-      </c>
-      <c r="E183" s="11" cm="1">
-        <f t="array" ref="E183">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.3E-3</v>
-      </c>
-      <c r="F183" s="11" t="str" cm="1">
-        <f t="array" ref="F183">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Cotton</v>
-      </c>
-      <c r="G183" s="11" t="str" cm="1">
-        <f t="array" ref="G183">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="H183" s="11" t="str" cm="1">
-        <f t="array" ref="H183">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+      <c r="D183" s="13" t="str">
+        <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
     <row r="184" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D184" s="11" t="str" cm="1">
-        <f t="array" ref="D184">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Horticultural crops</v>
-      </c>
-      <c r="E184" s="11" cm="1">
-        <f t="array" ref="E184">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="F184" s="11" t="str" cm="1">
-        <f t="array" ref="F184">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Horticultural crops</v>
-      </c>
-      <c r="G184" s="11" t="str" cm="1">
-        <f t="array" ref="G184">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="H184" s="11" t="str" cm="1">
-        <f t="array" ref="H184">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+      <c r="D184" s="13" t="str">
+        <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
     <row r="185" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D185" s="11" t="str" cm="1">
-        <f t="array" ref="D185">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice (continuous flooding)</v>
-      </c>
-      <c r="E185" s="11" cm="1">
-        <f t="array" ref="E185">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="F185" s="11" t="str" cm="1">
-        <f t="array" ref="F185">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice</v>
-      </c>
-      <c r="G185" s="11" t="str" cm="1">
-        <f t="array" ref="G185">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Continuous flooding</v>
-      </c>
-      <c r="H185" s="11" t="str" cm="1">
-        <f t="array" ref="H185">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+      <c r="D185" s="13" t="str">
+        <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
     <row r="186" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D186" s="11" t="str" cm="1">
-        <f t="array" ref="D186">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
-      </c>
-      <c r="E186" s="11" cm="1">
-        <f t="array" ref="E186">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F186" s="11" t="str" cm="1">
-        <f t="array" ref="F186">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice</v>
-      </c>
-      <c r="G186" s="11" t="str" cm="1">
-        <f t="array" ref="G186">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Single and multiple drainage, or alternate wetting and drying</v>
-      </c>
-      <c r="H186" s="11" t="str" cm="1">
-        <f t="array" ref="H186">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+      <c r="D186" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E186" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F186" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G186" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H186" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="187" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="11" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Aquaculture</v>
+        <v>Irrigated pasture</v>
       </c>
       <c r="E187" s="11" cm="1">
         <f t="array" ref="E187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>2.5999999999999999E-3</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="F187" s="11" t="str" cm="1">
         <f t="array" ref="F187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Aquaculture</v>
+        <v>Pasture</v>
       </c>
       <c r="G187" s="11" t="str" cm="1">
         <f t="array" ref="G187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
@@ -4580,15 +4474,15 @@
     <row r="188" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="11" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Forestry</v>
+        <v>Irrigated crop</v>
       </c>
       <c r="E188" s="11" cm="1">
         <f t="array" ref="E188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F188" s="11" t="str" cm="1">
         <f t="array" ref="F188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Forestry</v>
+        <v>Crop</v>
       </c>
       <c r="G188" s="11" t="str" cm="1">
         <f t="array" ref="G188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
@@ -4599,17 +4493,251 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D189" s="11" t="str" cm="1">
+        <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated pasture</v>
+      </c>
+      <c r="E189" s="11" cm="1">
+        <f t="array" ref="E189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="F189" s="11" t="str" cm="1">
+        <f t="array" ref="F189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Pasture</v>
+      </c>
+      <c r="G189" s="11" t="str" cm="1">
+        <f t="array" ref="G189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H189" s="11" t="str" cm="1">
+        <f t="array" ref="H189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Low rainfall</v>
+      </c>
+    </row>
+    <row r="190" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D190" s="11" t="str" cm="1">
+        <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated pasture</v>
+      </c>
+      <c r="E190" s="11" cm="1">
+        <f t="array" ref="E190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="F190" s="11" t="str" cm="1">
+        <f t="array" ref="F190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Pasture</v>
+      </c>
+      <c r="G190" s="11" t="str" cm="1">
+        <f t="array" ref="G190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H190" s="11" t="str" cm="1">
+        <f t="array" ref="H190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>High rainfall</v>
+      </c>
+    </row>
+    <row r="191" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D191" s="11" t="str" cm="1">
+        <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated crop (low rainfall)</v>
+      </c>
+      <c r="E191" s="11" cm="1">
+        <f t="array" ref="E191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="F191" s="11" t="str" cm="1">
+        <f t="array" ref="F191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Crop</v>
+      </c>
+      <c r="G191" s="11" t="str" cm="1">
+        <f t="array" ref="G191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H191" s="11" t="str" cm="1">
+        <f t="array" ref="H191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Low rainfall</v>
+      </c>
+    </row>
+    <row r="192" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D192" s="11" t="str" cm="1">
+        <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated crop (high rainfall)</v>
+      </c>
+      <c r="E192" s="11" cm="1">
+        <f t="array" ref="E192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F192" s="11" t="str" cm="1">
+        <f t="array" ref="F192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Crop</v>
+      </c>
+      <c r="G192" s="11" t="str" cm="1">
+        <f t="array" ref="G192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H192" s="11" t="str" cm="1">
+        <f t="array" ref="H192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>High rainfall</v>
+      </c>
+    </row>
+    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D193" s="11" t="str" cm="1">
+        <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Sugar</v>
+      </c>
+      <c r="E193" s="11" cm="1">
+        <f t="array" ref="E193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="F193" s="11" t="str" cm="1">
+        <f t="array" ref="F193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Sugar</v>
+      </c>
+      <c r="G193" s="11" t="str" cm="1">
+        <f t="array" ref="G193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H193" s="11" t="str" cm="1">
+        <f t="array" ref="H193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D194" s="11" t="str" cm="1">
+        <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Cotton</v>
+      </c>
+      <c r="E194" s="11" cm="1">
+        <f t="array" ref="E194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>5.3E-3</v>
+      </c>
+      <c r="F194" s="11" t="str" cm="1">
+        <f t="array" ref="F194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Cotton</v>
+      </c>
+      <c r="G194" s="11" t="str" cm="1">
+        <f t="array" ref="G194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H194" s="11" t="str" cm="1">
+        <f t="array" ref="H194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D195" s="11" t="str" cm="1">
+        <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Horticultural crops</v>
+      </c>
+      <c r="E195" s="11" cm="1">
+        <f t="array" ref="E195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="F195" s="11" t="str" cm="1">
+        <f t="array" ref="F195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Horticultural crops</v>
+      </c>
+      <c r="G195" s="11" t="str" cm="1">
+        <f t="array" ref="G195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H195" s="11" t="str" cm="1">
+        <f t="array" ref="H195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D196" s="11" t="str" cm="1">
+        <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice (continuous flooding)</v>
+      </c>
+      <c r="E196" s="11" cm="1">
+        <f t="array" ref="E196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="F196" s="11" t="str" cm="1">
+        <f t="array" ref="F196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice</v>
+      </c>
+      <c r="G196" s="11" t="str" cm="1">
+        <f t="array" ref="G196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Continuous flooding</v>
+      </c>
+      <c r="H196" s="11" t="str" cm="1">
+        <f t="array" ref="H196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D197" s="11" t="str" cm="1">
+        <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
+      </c>
+      <c r="E197" s="11" cm="1">
+        <f t="array" ref="E197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F197" s="11" t="str" cm="1">
+        <f t="array" ref="F197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice</v>
+      </c>
+      <c r="G197" s="11" t="str" cm="1">
+        <f t="array" ref="G197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Single and multiple drainage, or alternate wetting and drying</v>
+      </c>
+      <c r="H197" s="11" t="str" cm="1">
+        <f t="array" ref="H197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D198" s="11" t="str" cm="1">
+        <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Aquaculture</v>
+      </c>
+      <c r="E198" s="11" cm="1">
+        <f t="array" ref="E198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F198" s="11" t="str" cm="1">
+        <f t="array" ref="F198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Aquaculture</v>
+      </c>
+      <c r="G198" s="11" t="str" cm="1">
+        <f t="array" ref="G198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H198" s="11" t="str" cm="1">
+        <f t="array" ref="H198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D199" s="11" t="str" cm="1">
+        <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Forestry</v>
+      </c>
+      <c r="E199" s="11" cm="1">
+        <f t="array" ref="E199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="F199" s="11" t="str" cm="1">
+        <f t="array" ref="F199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Forestry</v>
+      </c>
+      <c r="G199" s="11" t="str" cm="1">
+        <f t="array" ref="G199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H199" s="11" t="str" cm="1">
+        <f t="array" ref="H199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="12">
+  <tableParts count="13">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -4622,6 +4750,7 @@
     <tablePart r:id="rId10"/>
     <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4651,21 +4780,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAgACAALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -4860,6 +4974,21 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACAAIAAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgACcAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQAnACwAIAAnAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAJwAgAGEAbgBkACAAJwBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAJwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIAAnAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlACcAIAByAG8AdwAgAHcAaQB0AGgAIABzAGEAbQBlACAARQBGACAAZgBvAHIAIABsAG8AdwAgAGEAbgBkACAAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcAG4ASQBQAEMAQwA6ACAATgAyAE8AIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABNAEEATgBBAEcARQBEACAAUwBPAEkATABTACwAIABBAE4ARAAgAEMATwAyACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATABJAE0ARQAgAEEATgBEACAAVQBSAEUAQQAgAEEAUABQAEwASQBDAEEAVABJAE8ATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAVwBFAFQAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBQAEMAQwAgADIAMAAxADkAIABSAGUAZgBpAG4AZQBtAGUAbgB0ACAAVgBvAGwAdQBtAGUAIAA0ADoAIABDAGgAYQBwAHQAZQByACAAMQAxADoAIABOADIATwAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0AYQBuAGEAZwBlAGQAIABTAG8AaQBsAHMALAAgAGEAbgBkACAAQwBPADIAIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABMAGkAbQBlACAAYQBuAGQAIABVAHIAZQBhACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHAAcgBpAG4AawBsAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQByAGYAYQBjAGUAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFQAYQBiAGwAZQAgAGMAcgBlAGEAdABlAGQAIABiAGEAcwBlAGQAIABvAG4AIABWAEUARQBSAEcAIAB0AGUAeAB0ACAAJwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgAnAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwAdAA+ADwAcwA+AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAPAAvAHMAPgA8AHMAPgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AC8AcwA+ADwALwB0AD4AXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApADwAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQA8AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAPgA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPAA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA+AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApADwAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAPgA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApADwAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQA+AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
@@ -4869,9 +4998,20 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4888,20 +5028,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/Common_v02.xlsx
+++ b/Excel/Common_v02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9154B3-3CE5-4AE1-8EED-CCC3765E414D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E96CC2B-52B5-4EE3-B37A-A2D092A4E89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="570" yWindow="345" windowWidth="37755" windowHeight="20445" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
@@ -90,6 +90,12 @@
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title">_xlfn.LAMBDA("Emission factor for urine and dung deposited on pasture, range or paddock")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
@@ -119,6 +125,12 @@
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Source">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Title">_xlfn.LAMBDA("Months to Seasons Mapping")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Title">_xlfn.LAMBDA("VEERG Australian rainfall zones")</definedName>
@@ -238,7 +250,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
   <si>
     <t>Climate zone</t>
   </si>
@@ -379,6 +391,15 @@
   </si>
   <si>
     <t>Irrigation type i</t>
+  </si>
+  <si>
+    <t>EFPRP</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Season</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1028,55 @@
     <cellStyle name="Unit no indent" xfId="53" xr:uid="{2829D020-DAD8-4B7D-9262-450720E27D2B}"/>
     <cellStyle name="Unit total" xfId="25" xr:uid="{65428923-3DAD-47B6-8DDF-0EBD05E7C55B}"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1642,20 +1711,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="29"/>
-      <tableStyleElement type="headerRow" dxfId="28"/>
-      <tableStyleElement type="totalRow" dxfId="27"/>
-      <tableStyleElement type="firstColumn" dxfId="26"/>
-      <tableStyleElement type="firstRowStripe" dxfId="25"/>
-      <tableStyleElement type="secondRowStripe" dxfId="24"/>
+      <tableStyleElement type="wholeTable" dxfId="31"/>
+      <tableStyleElement type="headerRow" dxfId="30"/>
+      <tableStyleElement type="totalRow" dxfId="29"/>
+      <tableStyleElement type="firstColumn" dxfId="28"/>
+      <tableStyleElement type="firstRowStripe" dxfId="27"/>
+      <tableStyleElement type="secondRowStripe" dxfId="26"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="23"/>
-      <tableStyleElement type="headerRow" dxfId="22"/>
-      <tableStyleElement type="totalRow" dxfId="21"/>
-      <tableStyleElement type="firstColumn" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
+      <tableStyleElement type="wholeTable" dxfId="25"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="totalRow" dxfId="23"/>
+      <tableStyleElement type="firstColumn" dxfId="22"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="secondRowStripe" dxfId="20"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -1798,7 +1867,7 @@
     <tableColumn id="1" xr3:uid="{CA74DB79-CAE7-4EF8-BA48-96421E9E9373}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="3">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1846,8 +1915,44 @@
     <tableColumn id="1" xr3:uid="{B18D772B-2FE9-457A-A200-8E17C55C340C}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+  <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{718360C9-DDF8-4B7B-B842-EE0D39ED743F}" name="Climate zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{876E0F1A-E7CF-4E69-9C3F-6E0E84FF4B5D}" name="EFPRP" dataDxfId="1" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+  <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7CBE043C-4D22-47C3-AE18-5E55E64542E1}" name="Month">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{10DA8C9D-4358-470A-AF6C-AE27470313DE}" name="Season" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1940,49 +2045,49 @@
     <tableColumn id="1" xr3:uid="{8938BBE8-7B92-48A9-872B-3320D21DB635}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="17" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="16" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="18" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="15" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="17" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="14" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="16" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="13" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="15" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="12" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="14" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="11" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="13" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="10" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="12" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="9" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="11" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="8" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="10" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="7" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="9" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="6" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="8" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="5" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="7" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="4" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="6" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="3" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="5" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2000,7 +2105,7 @@
     <tableColumn id="1" xr3:uid="{2FCD4A06-823B-4A3F-89D0-46C27A9E1AA9}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="2" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="4" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2348,7 +2453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83968956-F921-4291-AAEE-DE11952DD430}">
-  <dimension ref="A1:BX199"/>
+  <dimension ref="A1:BX224"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
@@ -4735,9 +4840,195 @@
         <v>Any</v>
       </c>
     </row>
+    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D202" s="5" t="str" cm="1">
+        <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
+        <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
+      </c>
+    </row>
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D203" s="4" t="str" cm="1">
+        <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
+        <v>VEERG 2026: Table A.2.2.2</v>
+      </c>
+    </row>
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D204" s="13" t="str" cm="1">
+        <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
+        <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
+      </c>
+    </row>
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D205" s="12" t="str" cm="1">
+        <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D206" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E206" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D207" s="14" t="str" cm="1">
+        <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E207" s="14" cm="1">
+        <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D208" s="1" t="str" cm="1">
+        <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E208" s="11" cm="1">
+        <f t="array" ref="E208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D211" s="1" t="str" cm="1">
+        <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
+        <v>Months to Seasons Mapping</v>
+      </c>
+    </row>
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D212" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E212" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D213" s="14" t="str" cm="1">
+        <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>January</v>
+      </c>
+      <c r="E213" s="14" t="str" cm="1">
+        <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Summer</v>
+      </c>
+    </row>
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D214" s="1" t="str" cm="1">
+        <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>February</v>
+      </c>
+      <c r="E214" s="11" t="str" cm="1">
+        <f t="array" ref="E214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Summer</v>
+      </c>
+    </row>
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D215" s="1" t="str" cm="1">
+        <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>March</v>
+      </c>
+      <c r="E215" s="11" t="str" cm="1">
+        <f t="array" ref="E215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Autumn</v>
+      </c>
+    </row>
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D216" s="1" t="str" cm="1">
+        <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>April</v>
+      </c>
+      <c r="E216" s="11" t="str" cm="1">
+        <f t="array" ref="E216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Autumn</v>
+      </c>
+    </row>
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D217" s="1" t="str" cm="1">
+        <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>May</v>
+      </c>
+      <c r="E217" s="11" t="str" cm="1">
+        <f t="array" ref="E217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Autumn</v>
+      </c>
+    </row>
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D218" s="1" t="str" cm="1">
+        <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>June</v>
+      </c>
+      <c r="E218" s="11" t="str" cm="1">
+        <f t="array" ref="E218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Winter</v>
+      </c>
+    </row>
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D219" s="1" t="str" cm="1">
+        <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>July</v>
+      </c>
+      <c r="E219" s="11" t="str" cm="1">
+        <f t="array" ref="E219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Winter</v>
+      </c>
+    </row>
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D220" s="1" t="str" cm="1">
+        <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>August</v>
+      </c>
+      <c r="E220" s="11" t="str" cm="1">
+        <f t="array" ref="E220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Winter</v>
+      </c>
+    </row>
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D221" s="1" t="str" cm="1">
+        <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>September</v>
+      </c>
+      <c r="E221" s="11" t="str" cm="1">
+        <f t="array" ref="E221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Spring</v>
+      </c>
+    </row>
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D222" s="1" t="str" cm="1">
+        <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>October</v>
+      </c>
+      <c r="E222" s="11" t="str" cm="1">
+        <f t="array" ref="E222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Spring</v>
+      </c>
+    </row>
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D223" s="1" t="str" cm="1">
+        <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>November</v>
+      </c>
+      <c r="E223" s="11" t="str" cm="1">
+        <f t="array" ref="E223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Spring</v>
+      </c>
+    </row>
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D224" s="1" t="str" cm="1">
+        <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>December</v>
+      </c>
+      <c r="E224" s="11" t="str" cm="1">
+        <f t="array" ref="E224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Summer</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="13">
+  <tableParts count="15">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -4751,6 +5042,8 @@
     <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4986,7 +5279,7 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACAAIAAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgACcAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQAnACwAIAAnAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAJwAgAGEAbgBkACAAJwBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAJwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIAAnAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlACcAIAByAG8AdwAgAHcAaQB0AGgAIABzAGEAbQBlACAARQBGACAAZgBvAHIAIABsAG8AdwAgAGEAbgBkACAAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcAG4ASQBQAEMAQwA6ACAATgAyAE8AIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABNAEEATgBBAEcARQBEACAAUwBPAEkATABTACwAIABBAE4ARAAgAEMATwAyACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATABJAE0ARQAgAEEATgBEACAAVQBSAEUAQQAgAEEAUABQAEwASQBDAEEAVABJAE8ATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAVwBFAFQAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBQAEMAQwAgADIAMAAxADkAIABSAGUAZgBpAG4AZQBtAGUAbgB0ACAAVgBvAGwAdQBtAGUAIAA0ADoAIABDAGgAYQBwAHQAZQByACAAMQAxADoAIABOADIATwAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0AYQBuAGEAZwBlAGQAIABTAG8AaQBsAHMALAAgAGEAbgBkACAAQwBPADIAIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABMAGkAbQBlACAAYQBuAGQAIABVAHIAZQBhACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHAAcgBpAG4AawBsAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQByAGYAYQBjAGUAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFQAYQBiAGwAZQAgAGMAcgBlAGEAdABlAGQAIABiAGEAcwBlAGQAIABvAG4AIABWAEUARQBSAEcAIAB0AGUAeAB0ACAAJwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgAnAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwAdAA+ADwAcwA+AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAPAAvAHMAPgA8AHMAPgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AC8AcwA+ADwALwB0AD4AXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApADwAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQA8AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAPgA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPAA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA+AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApADwAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAPgA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApADwAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQA+AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwAdAA+ADwAcwA+AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAPAAvAHMAPgA8AHMAPgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AC8AcwA+ADwALwB0AD4AXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApADwAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQA8AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAPgA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPAA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA+AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApADwAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAPgA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApADwAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQA+AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/Common_v02.xlsx
+++ b/Excel/Common_v02.xlsx
@@ -5279,7 +5279,7 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwAdAA+ADwAcwA+AFwAIgAgACYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAPAAvAHMAPgA8AHMAPgBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AC8AcwA+ADwALwB0AD4AXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApADwAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQA+AD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQA8AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAPgA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPAA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA+AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApADwAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAPgA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApADwAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQA+AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/Common_v02.xlsx
+++ b/Excel/Common_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E96CC2B-52B5-4EE3-B37A-A2D092A4E89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6FEFB5-2EBA-45CB-AFD0-37A0943ACDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="345" windowWidth="37755" windowHeight="20445" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="-30" yWindow="105" windowWidth="28875" windowHeight="16890" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="3" r:id="rId1"/>
@@ -32,9 +32,11 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
@@ -44,6 +46,8 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -125,6 +129,11 @@
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Source">_xlfn.LAMBDA("")</definedName>
@@ -173,6 +182,7 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
     <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
@@ -250,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>Climate zone</t>
   </si>
@@ -400,6 +410,54 @@
   </si>
   <si>
     <t>Season</t>
+  </si>
+  <si>
+    <t>Temperature zone</t>
+  </si>
+  <si>
+    <t>Anaerobic lagoon</t>
+  </si>
+  <si>
+    <t>Digester / covered lagoons</t>
+  </si>
+  <si>
+    <t>Liquid systems</t>
+  </si>
+  <si>
+    <t>Daily spread</t>
+  </si>
+  <si>
+    <t>Composting (passive windrow)</t>
+  </si>
+  <si>
+    <t>Solid storage</t>
+  </si>
+  <si>
+    <t>Pit storage</t>
+  </si>
+  <si>
+    <t>Deep litter</t>
+  </si>
+  <si>
+    <t>Poultry manure with bedding</t>
+  </si>
+  <si>
+    <t>Poultry manure without bedding</t>
+  </si>
+  <si>
+    <t>Direct processing</t>
+  </si>
+  <si>
+    <t>Direct application</t>
+  </si>
+  <si>
+    <t>Pasture range and paddock</t>
+  </si>
+  <si>
+    <t>MAT (ºC)</t>
+  </si>
+  <si>
+    <t>MAT raw</t>
   </si>
 </sst>
 </file>
@@ -926,7 +984,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -964,6 +1022,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,7 +1089,367 @@
     <cellStyle name="Unit no indent" xfId="53" xr:uid="{2829D020-DAD8-4B7D-9262-450720E27D2B}"/>
     <cellStyle name="Unit total" xfId="25" xr:uid="{65428923-3DAD-47B6-8DDF-0EBD05E7C55B}"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="47">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1711,20 +2132,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="31"/>
-      <tableStyleElement type="headerRow" dxfId="30"/>
-      <tableStyleElement type="totalRow" dxfId="29"/>
-      <tableStyleElement type="firstColumn" dxfId="28"/>
-      <tableStyleElement type="firstRowStripe" dxfId="27"/>
-      <tableStyleElement type="secondRowStripe" dxfId="26"/>
+      <tableStyleElement type="wholeTable" dxfId="46"/>
+      <tableStyleElement type="headerRow" dxfId="45"/>
+      <tableStyleElement type="totalRow" dxfId="44"/>
+      <tableStyleElement type="firstColumn" dxfId="43"/>
+      <tableStyleElement type="firstRowStripe" dxfId="42"/>
+      <tableStyleElement type="secondRowStripe" dxfId="41"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="25"/>
-      <tableStyleElement type="headerRow" dxfId="24"/>
-      <tableStyleElement type="totalRow" dxfId="23"/>
-      <tableStyleElement type="firstColumn" dxfId="22"/>
-      <tableStyleElement type="firstRowStripe" dxfId="21"/>
-      <tableStyleElement type="secondRowStripe" dxfId="20"/>
+      <tableStyleElement type="wholeTable" dxfId="40"/>
+      <tableStyleElement type="headerRow" dxfId="39"/>
+      <tableStyleElement type="totalRow" dxfId="38"/>
+      <tableStyleElement type="firstColumn" dxfId="37"/>
+      <tableStyleElement type="firstRowStripe" dxfId="36"/>
+      <tableStyleElement type="secondRowStripe" dxfId="35"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -1867,7 +2288,7 @@
     <tableColumn id="1" xr3:uid="{CA74DB79-CAE7-4EF8-BA48-96421E9E9373}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="18">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1915,7 +2336,7 @@
     <tableColumn id="1" xr3:uid="{B18D772B-2FE9-457A-A200-8E17C55C340C}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1933,7 +2354,7 @@
     <tableColumn id="1" xr3:uid="{718360C9-DDF8-4B7B-B842-EE0D39ED743F}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{876E0F1A-E7CF-4E69-9C3F-6E0E84FF4B5D}" name="EFPRP" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{876E0F1A-E7CF-4E69-9C3F-6E0E84FF4B5D}" name="EFPRP" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1951,8 +2372,82 @@
     <tableColumn id="1" xr3:uid="{7CBE043C-4D22-47C3-AE18-5E55E64542E1}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{10DA8C9D-4358-470A-AF6C-AE27470313DE}" name="Season" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{10DA8C9D-4358-470A-AF6C-AE27470313DE}" name="Season" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+  <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{8E03AF9F-C6DD-415E-A42C-F2360BC32F72}" name="Temperature zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{07B3EB32-B4EC-4553-A2E1-8AE19F5ED1B8}" name="MAT (ºC)" dataDxfId="14" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{D245CE73-83DF-4AB6-BE51-10D787832614}" name="Anaerobic lagoon" dataDxfId="13" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{96977D75-8628-4103-9D52-F7049CB2572B}" name="Digester / covered lagoons" dataDxfId="12" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{F64B281A-2EA4-4881-94F1-FEBD2B18C677}" name="Liquid systems" dataDxfId="11" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{8934BA44-DDF5-433B-A89F-5DB281BAB7B5}" name="Daily spread" dataDxfId="10" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{699EC0ED-651C-48B9-9F8F-73146B12DB72}" name="Composting (passive windrow)" dataDxfId="9" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{6E240578-9A8B-47C9-A356-B69BB058D44B}" name="Solid storage" dataDxfId="8" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{922DD34E-8EDF-42D6-BE68-8D30A5F4A8CF}" name="Pit storage" dataDxfId="7" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{730FA508-F44F-43A0-8A87-F28C2DB6D4D5}" name="Deep litter" dataDxfId="6" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{8BD6E90D-D2CF-4733-8286-F67C28172389}" name="Poultry manure with bedding" dataDxfId="5" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{EE74F5BC-4374-40FF-85F0-AE26E403B07E}" name="Poultry manure without bedding" dataDxfId="4" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{B53034D9-4966-41B7-BD99-44BBB861677D}" name="Direct processing" dataDxfId="3" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{59F06DF1-1149-43CE-9ADC-FD2C1D44B8D0}" name="Direct application" dataDxfId="2" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{E8CF9642-D223-420C-B387-277C82D3BB2E}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{0B403FCE-8D29-4E28-99ED-B0004709790F}" name="MAT raw" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2045,49 +2540,49 @@
     <tableColumn id="1" xr3:uid="{8938BBE8-7B92-48A9-872B-3320D21DB635}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="18" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="17" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="16" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="15" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="14" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="13" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="12" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="11" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="10" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="9" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="8" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="7" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="6" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="5" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2105,7 +2600,7 @@
     <tableColumn id="1" xr3:uid="{2FCD4A06-823B-4A3F-89D0-46C27A9E1AA9}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="4" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2406,7 +2901,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="984" row="3">
+  <wetp:taskpane dockstate="right" visibility="0" width="825" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2453,25 +2948,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83968956-F921-4291-AAEE-DE11952DD430}">
-  <dimension ref="A1:BX224"/>
+  <dimension ref="A1:BY250"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="6" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="48" style="1" customWidth="1"/>
-    <col min="5" max="16" width="20.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" style="1" customWidth="1"/>
-    <col min="18" max="19" width="20.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="4.7109375" style="1" customWidth="1"/>
-    <col min="21" max="32" width="20.7109375" style="6" customWidth="1"/>
-    <col min="33" max="38" width="21.85546875" style="6" customWidth="1"/>
-    <col min="39" max="43" width="20.7109375" style="6" customWidth="1"/>
-    <col min="44" max="64" width="9.140625" style="6"/>
-    <col min="65" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="6" width="20.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="34.28515625" style="1" customWidth="1"/>
+    <col min="11" max="13" width="20.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="33.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="36.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21" style="1" customWidth="1"/>
+    <col min="17" max="17" width="21.28515625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.140625" style="1" customWidth="1"/>
+    <col min="19" max="20" width="20.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" style="1" customWidth="1"/>
+    <col min="22" max="33" width="20.7109375" style="6" customWidth="1"/>
+    <col min="34" max="39" width="21.85546875" style="6" customWidth="1"/>
+    <col min="40" max="44" width="20.7109375" style="6" customWidth="1"/>
+    <col min="45" max="65" width="9.140625" style="6"/>
+    <col min="66" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:65" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -2479,8 +2982,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:64" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2500,22 +3003,23 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="9"/>
+      <c r="U3" s="3"/>
       <c r="V3" s="9"/>
-    </row>
-    <row r="4" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W3" s="9"/>
+    </row>
+    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
-      <c r="BL4" s="2"/>
-    </row>
-    <row r="5" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM4" s="2"/>
+    </row>
+    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="5" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
       </c>
-      <c r="BL5" s="2"/>
-    </row>
-    <row r="6" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM5" s="2"/>
+    </row>
+    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="D6" s="11" t="s">
         <v>1</v>
@@ -2527,7 +3031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="D7" s="11" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2542,7 +3046,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8"/>
       <c r="D8" s="11" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2557,7 +3061,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="11" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2572,7 +3076,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="11" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2587,7 +3091,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="11" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2601,9 +3105,9 @@
         <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>SA</v>
       </c>
-      <c r="BL11" s="2"/>
-    </row>
-    <row r="12" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM11" s="2"/>
+    </row>
+    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="11" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2617,9 +3121,9 @@
         <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>WA</v>
       </c>
-      <c r="BL12" s="2"/>
-    </row>
-    <row r="13" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM12" s="2"/>
+    </row>
+    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="11" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2634,7 +3138,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="11" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -2649,10 +3153,10 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3221,46 +3725,46 @@
     <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="5" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="4" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="13" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="13" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="13" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="13" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="13" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="11" t="s">
         <v>0</v>
       </c>
@@ -3309,8 +3813,9 @@
       <c r="S89" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="90" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T89" s="11"/>
+    </row>
+    <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="11" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
@@ -3375,8 +3880,9 @@
         <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="91" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T90" s="11"/>
+    </row>
+    <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="11" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
@@ -3441,8 +3947,9 @@
         <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="92" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T91" s="11"/>
+    </row>
+    <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="11" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
@@ -3507,8 +4014,9 @@
         <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="93" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T92" s="11"/>
+    </row>
+    <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="11" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
@@ -3573,8 +4081,9 @@
         <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="94" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T93" s="11"/>
+    </row>
+    <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D94" s="11" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
@@ -3639,8 +4148,9 @@
         <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="95" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T94" s="11"/>
+    </row>
+    <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D95" s="11" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
@@ -3705,8 +4215,9 @@
         <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T95" s="11"/>
+    </row>
+    <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="11" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
@@ -3771,8 +4282,9 @@
         <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="97" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T96" s="11"/>
+    </row>
+    <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="11" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
@@ -3837,53 +4349,54 @@
         <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T97" s="11"/>
+    </row>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="12" t="str" cm="1">
         <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="99" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="12" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="100" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="12" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="101" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="12" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="12"/>
     </row>
-    <row r="103" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="5" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D106" s="4" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="13" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="11" t="s">
         <v>27</v>
       </c>
@@ -3897,7 +4410,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="110" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D110" s="11" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Warm</v>
@@ -3915,7 +4428,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D111" s="11" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Temperate</v>
@@ -3933,7 +4446,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D112" s="11" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Cool</v>
@@ -3951,33 +4464,33 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="5" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
         <v>VEERG Australian rainfall zones</v>
       </c>
-      <c r="BM115" s="6"/>
-    </row>
-    <row r="116" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN115" s="6"/>
+    </row>
+    <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="4" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
-      <c r="BM116" s="6"/>
-    </row>
-    <row r="117" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN116" s="6"/>
+    </row>
+    <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="13" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
-      <c r="BM117" s="6"/>
-    </row>
-    <row r="118" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM118" s="6"/>
-    </row>
-    <row r="119" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN117" s="6"/>
+    </row>
+    <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN118" s="6"/>
+    </row>
+    <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="11" t="s">
         <v>30</v>
       </c>
@@ -3990,9 +4503,9 @@
       <c r="G119" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="BM119" s="6"/>
-    </row>
-    <row r="120" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN119" s="6"/>
+    </row>
+    <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="11" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>High rainfall</v>
@@ -4009,9 +4522,9 @@
         <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>999999</v>
       </c>
-      <c r="BM120" s="6"/>
-    </row>
-    <row r="121" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN120" s="6"/>
+    </row>
+    <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="11" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Low rainfall</v>
@@ -4028,26 +4541,26 @@
         <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600</v>
       </c>
-      <c r="BM121" s="6"/>
-    </row>
-    <row r="122" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM122" s="6"/>
-    </row>
-    <row r="123" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN121" s="6"/>
+    </row>
+    <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN122" s="6"/>
+    </row>
+    <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="5" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D125" s="4" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="11" t="s">
         <v>32</v>
       </c>
@@ -4055,7 +4568,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="11" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching occurs</v>
@@ -4065,7 +4578,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D129" s="11" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching does not occur</v>
@@ -4075,23 +4588,23 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D132" s="5" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E132" s="10"/>
     </row>
-    <row r="133" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D133" s="4" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E133" s="10"/>
     </row>
-    <row r="134" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" t="s">
         <v>37</v>
       </c>
@@ -4099,7 +4612,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>Yes - in leaching zone</v>
@@ -4109,7 +4622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>No - not in leaching zone</v>
@@ -4119,9 +4632,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM138" s="6"/>
+    <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN138" s="6"/>
       <c r="BO138" s="6"/>
       <c r="BP138" s="6"/>
@@ -4133,13 +4645,13 @@
       <c r="BV138" s="6"/>
       <c r="BW138" s="6"/>
       <c r="BX138" s="6"/>
-    </row>
-    <row r="139" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BY138" s="6"/>
+    </row>
+    <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="5" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
         <v>FracWET for irrigation types</v>
       </c>
-      <c r="BM139" s="6"/>
       <c r="BN139" s="6"/>
       <c r="BO139" s="6"/>
       <c r="BP139" s="6"/>
@@ -4151,13 +4663,13 @@
       <c r="BV139" s="6"/>
       <c r="BW139" s="6"/>
       <c r="BX139" s="6"/>
-    </row>
-    <row r="140" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BY139" s="6"/>
+    </row>
+    <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D140" s="4" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
         <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
       </c>
-      <c r="BM140" s="6"/>
       <c r="BN140" s="6"/>
       <c r="BO140" s="6"/>
       <c r="BP140" s="6"/>
@@ -4169,35 +4681,36 @@
       <c r="BV140" s="6"/>
       <c r="BW140" s="6"/>
       <c r="BX140" s="6"/>
-    </row>
-    <row r="141" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BY140" s="6"/>
+    </row>
+    <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D141" s="13" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
-      <c r="BM141" s="6"/>
-    </row>
-    <row r="142" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D142" s="14" t="s">
+      <c r="BN141" s="6"/>
+    </row>
+    <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D142" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E142" s="14" t="s">
+      <c r="E142" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="BM142" s="6"/>
-    </row>
-    <row r="143" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D143" s="14" t="str" cm="1">
+      <c r="BN142" s="6"/>
+    </row>
+    <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D143" s="11" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="E143" s="14" cm="1">
+      <c r="E143" s="11" cm="1">
         <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BM143" s="6"/>
-    </row>
-    <row r="144" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN143" s="6"/>
+    </row>
+    <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Drip irrigation</v>
@@ -4206,9 +4719,9 @@
         <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BM144" s="6"/>
-    </row>
-    <row r="145" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN144" s="6"/>
+    </row>
+    <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Sprinkler irrigation</v>
@@ -4217,9 +4730,9 @@
         <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BM145" s="6"/>
-    </row>
-    <row r="146" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN145" s="6"/>
+    </row>
+    <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Surface irrigation</v>
@@ -4228,9 +4741,9 @@
         <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BM146" s="6"/>
-    </row>
-    <row r="147" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN146" s="6"/>
+    </row>
+    <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Other irrigation</v>
@@ -4239,39 +4752,38 @@
         <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BM147" s="6"/>
-    </row>
-    <row r="148" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM148" s="6"/>
-    </row>
-    <row r="149" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM149" s="6"/>
-    </row>
-    <row r="150" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN147" s="6"/>
+    </row>
+    <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN148" s="6"/>
+    </row>
+    <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN149" s="6"/>
+    </row>
+    <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="5" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
         <v>Australian data scores for scope 3</v>
       </c>
-      <c r="BM150" s="6"/>
-    </row>
-    <row r="151" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN150" s="6"/>
+    </row>
+    <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="4" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
         <v>VEERG 2026: XXXXXXXX</v>
       </c>
-      <c r="BM151" s="6"/>
-    </row>
-    <row r="152" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM152" s="6"/>
-    </row>
-    <row r="153" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN151" s="6"/>
+    </row>
+    <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN152" s="6"/>
+    </row>
+    <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D153" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E153" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="BB153" s="2"/>
       <c r="BC153" s="2"/>
       <c r="BD153" s="2"/>
       <c r="BE153" s="2"/>
@@ -4282,8 +4794,9 @@
       <c r="BJ153" s="2"/>
       <c r="BK153" s="2"/>
       <c r="BL153" s="2"/>
-    </row>
-    <row r="154" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM153" s="2"/>
+    </row>
+    <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D154" s="11" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>International scope 3 database</v>
@@ -4292,7 +4805,6 @@
         <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BB154" s="2"/>
       <c r="BC154" s="2"/>
       <c r="BD154" s="2"/>
       <c r="BE154" s="2"/>
@@ -4303,8 +4815,9 @@
       <c r="BJ154" s="2"/>
       <c r="BK154" s="2"/>
       <c r="BL154" s="2"/>
-    </row>
-    <row r="155" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM154" s="2"/>
+    </row>
+    <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D155" s="11" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Australian scope 3 database</v>
@@ -4313,7 +4826,6 @@
         <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>2</v>
       </c>
-      <c r="BB155" s="2"/>
       <c r="BC155" s="2"/>
       <c r="BD155" s="2"/>
       <c r="BE155" s="2"/>
@@ -4324,8 +4836,9 @@
       <c r="BJ155" s="2"/>
       <c r="BK155" s="2"/>
       <c r="BL155" s="2"/>
-    </row>
-    <row r="156" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM155" s="2"/>
+    </row>
+    <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D156" s="11" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>State or regional scope 3 database</v>
@@ -4335,7 +4848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D157" s="11" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Emissions intensity calculated from approved method</v>
@@ -4345,7 +4858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D158" s="11" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Verified credential matching ISO14067</v>
@@ -4355,30 +4868,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="5" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="10"/>
     </row>
-    <row r="162" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="4" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="10"/>
     </row>
-    <row r="163" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="4" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="10"/>
     </row>
-    <row r="164" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="10" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -4387,44 +4900,44 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM165" s="6"/>
+    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="6"/>
       <c r="BO165" s="6"/>
-    </row>
-    <row r="166" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM166" s="6"/>
+      <c r="BP165" s="6"/>
+    </row>
+    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="6"/>
       <c r="BO166" s="6"/>
-    </row>
-    <row r="167" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP166" s="6"/>
+    </row>
+    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="5" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
       </c>
-      <c r="BM167" s="6"/>
       <c r="BN167" s="6"/>
       <c r="BO167" s="6"/>
-    </row>
-    <row r="168" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP167" s="6"/>
+    </row>
+    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="4" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
-      <c r="BM168" s="6"/>
       <c r="BN168" s="6"/>
       <c r="BO168" s="6"/>
-    </row>
-    <row r="169" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP168" s="6"/>
+    </row>
+    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="4" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
       </c>
-      <c r="BM169" s="6"/>
       <c r="BN169" s="6"/>
       <c r="BO169" s="6"/>
-    </row>
-    <row r="170" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP169" s="6"/>
+    </row>
+    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -4432,39 +4945,39 @@
       <c r="E170" s="1">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="BM170" s="6"/>
       <c r="BN170" s="6"/>
       <c r="BO170" s="6"/>
-    </row>
-    <row r="171" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM171" s="6"/>
+      <c r="BP170" s="6"/>
+    </row>
+    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="6"/>
       <c r="BO171" s="6"/>
-    </row>
-    <row r="172" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM172" s="6"/>
+      <c r="BP171" s="6"/>
+    </row>
+    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="6"/>
       <c r="BO172" s="6"/>
-    </row>
-    <row r="173" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP172" s="6"/>
+    </row>
+    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="5" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
       </c>
-      <c r="BM173" s="6"/>
       <c r="BN173" s="6"/>
       <c r="BO173" s="6"/>
-    </row>
-    <row r="174" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP173" s="6"/>
+    </row>
+    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="4" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
       </c>
-      <c r="BM174" s="6"/>
       <c r="BN174" s="6"/>
       <c r="BO174" s="6"/>
-    </row>
-    <row r="175" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP174" s="6"/>
+    </row>
+    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -4473,71 +4986,71 @@
         <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
         <v>kg/m3</v>
       </c>
-      <c r="BM175" s="6"/>
       <c r="BN175" s="6"/>
       <c r="BO175" s="6"/>
-    </row>
-    <row r="176" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM176" s="6"/>
+      <c r="BP175" s="6"/>
+    </row>
+    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="6"/>
       <c r="BO176" s="6"/>
-    </row>
-    <row r="177" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM177" s="6"/>
+      <c r="BP176" s="6"/>
+    </row>
+    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="6"/>
       <c r="BO177" s="6"/>
-    </row>
-    <row r="178" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP177" s="6"/>
+    </row>
+    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="5" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
       </c>
-      <c r="BM178" s="6"/>
       <c r="BN178" s="6"/>
       <c r="BO178" s="6"/>
-    </row>
-    <row r="179" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP178" s="6"/>
+    </row>
+    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="4" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
       </c>
-      <c r="BM179" s="6"/>
       <c r="BN179" s="6"/>
       <c r="BO179" s="6"/>
-    </row>
-    <row r="180" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP179" s="6"/>
+    </row>
+    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="12" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="13" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="13" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="13" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="13" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="13" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="11" t="s">
         <v>39</v>
       </c>
@@ -4554,7 +5067,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="11" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -4576,7 +5089,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="11" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -4598,7 +5111,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="11" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -4620,7 +5133,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="11" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -4642,7 +5155,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="11" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -4664,7 +5177,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="11" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -4865,19 +5378,19 @@
       </c>
     </row>
     <row r="206" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D206" s="14" t="s">
+      <c r="D206" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E206" s="14" t="s">
+      <c r="E206" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D207" s="14" t="str" cm="1">
+      <c r="D207" s="11" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E207" s="14" cm="1">
+      <c r="E207" s="11" cm="1">
         <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -4899,19 +5412,19 @@
       </c>
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D212" s="14" t="s">
+      <c r="D212" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E212" s="14" t="s">
+      <c r="E212" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D213" s="14" t="str" cm="1">
+      <c r="D213" s="11" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
       </c>
-      <c r="E213" s="14" t="str" cm="1">
+      <c r="E213" s="11" t="str" cm="1">
         <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -5026,10 +5539,1332 @@
         <v>Summer</v>
       </c>
     </row>
+    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D227" s="5" t="str" cm="1">
+        <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
+        <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
+      </c>
+    </row>
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D228" s="4" t="str" cm="1">
+        <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
+        <v>VEERG 2026: Table A.1.8.1</v>
+      </c>
+    </row>
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D229" s="13" t="str" cm="1">
+        <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
+        <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
+      </c>
+    </row>
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D231" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E231" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G231" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H231" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I231" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J231" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="K231" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L231" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M231" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="N231" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="O231" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="P231" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q231" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="R231" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="S231" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D232" s="14" t="str" cm="1">
+        <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E232" s="14" t="str" cm="1">
+        <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>≤10</v>
+      </c>
+      <c r="F232" s="14" cm="1">
+        <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.66</v>
+      </c>
+      <c r="G232" s="14" cm="1">
+        <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H232" s="14" cm="1">
+        <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="I232" s="14" cm="1">
+        <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J232" s="14" cm="1">
+        <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K232" s="14" cm="1">
+        <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L232" s="14" cm="1">
+        <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M232" s="14" cm="1">
+        <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N232" s="14" cm="1">
+        <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O232" s="14" cm="1">
+        <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P232" s="14" cm="1">
+        <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q232" s="14" cm="1">
+        <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R232" s="14" cm="1">
+        <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S232" s="14" cm="1">
+        <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D233" s="1" t="str" cm="1">
+        <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E233" s="11" cm="1">
+        <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>11</v>
+      </c>
+      <c r="F233" s="11" cm="1">
+        <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.68</v>
+      </c>
+      <c r="G233" s="11" cm="1">
+        <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H233" s="11" cm="1">
+        <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.11</v>
+      </c>
+      <c r="I233" s="11" cm="1">
+        <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J233" s="11" cm="1">
+        <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K233" s="11" cm="1">
+        <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L233" s="11" cm="1">
+        <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M233" s="11" cm="1">
+        <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N233" s="11" cm="1">
+        <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O233" s="11" cm="1">
+        <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P233" s="11" cm="1">
+        <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q233" s="11" cm="1">
+        <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R233" s="11" cm="1">
+        <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S233" s="14" cm="1">
+        <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D234" s="1" t="str" cm="1">
+        <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E234" s="11" cm="1">
+        <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>12</v>
+      </c>
+      <c r="F234" s="11" cm="1">
+        <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.7</v>
+      </c>
+      <c r="G234" s="11" cm="1">
+        <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H234" s="11" cm="1">
+        <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.13</v>
+      </c>
+      <c r="I234" s="11" cm="1">
+        <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J234" s="11" cm="1">
+        <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K234" s="11" cm="1">
+        <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L234" s="11" cm="1">
+        <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M234" s="11" cm="1">
+        <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N234" s="11" cm="1">
+        <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O234" s="11" cm="1">
+        <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P234" s="11" cm="1">
+        <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q234" s="11" cm="1">
+        <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R234" s="11" cm="1">
+        <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S234" s="14" cm="1">
+        <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D235" s="1" t="str" cm="1">
+        <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E235" s="11" cm="1">
+        <f t="array" ref="E235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>13</v>
+      </c>
+      <c r="F235" s="11" cm="1">
+        <f t="array" ref="F235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.71</v>
+      </c>
+      <c r="G235" s="11" cm="1">
+        <f t="array" ref="G235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H235" s="11" cm="1">
+        <f t="array" ref="H235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I235" s="11" cm="1">
+        <f t="array" ref="I235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J235" s="11" cm="1">
+        <f t="array" ref="J235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K235" s="11" cm="1">
+        <f t="array" ref="K235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L235" s="11" cm="1">
+        <f t="array" ref="L235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M235" s="11" cm="1">
+        <f t="array" ref="M235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N235" s="11" cm="1">
+        <f t="array" ref="N235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O235" s="11" cm="1">
+        <f t="array" ref="O235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P235" s="11" cm="1">
+        <f t="array" ref="P235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q235" s="11" cm="1">
+        <f t="array" ref="Q235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R235" s="11" cm="1">
+        <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S235" s="14" cm="1">
+        <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D236" s="1" t="str" cm="1">
+        <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E236" s="11" cm="1">
+        <f t="array" ref="E236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>14</v>
+      </c>
+      <c r="F236" s="11" cm="1">
+        <f t="array" ref="F236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.73</v>
+      </c>
+      <c r="G236" s="11" cm="1">
+        <f t="array" ref="G236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H236" s="11" cm="1">
+        <f t="array" ref="H236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.15</v>
+      </c>
+      <c r="I236" s="11" cm="1">
+        <f t="array" ref="I236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J236" s="11" cm="1">
+        <f t="array" ref="J236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K236" s="11" cm="1">
+        <f t="array" ref="K236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L236" s="11" cm="1">
+        <f t="array" ref="L236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M236" s="11" cm="1">
+        <f t="array" ref="M236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N236" s="11" cm="1">
+        <f t="array" ref="N236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O236" s="11" cm="1">
+        <f t="array" ref="O236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P236" s="11" cm="1">
+        <f t="array" ref="P236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q236" s="11" cm="1">
+        <f t="array" ref="Q236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R236" s="11" cm="1">
+        <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S236" s="14" cm="1">
+        <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D237" s="1" t="str" cm="1">
+        <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E237" s="11" cm="1">
+        <f t="array" ref="E237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>15</v>
+      </c>
+      <c r="F237" s="11" cm="1">
+        <f t="array" ref="F237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.74</v>
+      </c>
+      <c r="G237" s="11" cm="1">
+        <f t="array" ref="G237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H237" s="11" cm="1">
+        <f t="array" ref="H237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.17</v>
+      </c>
+      <c r="I237" s="11" cm="1">
+        <f t="array" ref="I237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J237" s="11" cm="1">
+        <f t="array" ref="J237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K237" s="11" cm="1">
+        <f t="array" ref="K237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L237" s="11" cm="1">
+        <f t="array" ref="L237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M237" s="11" cm="1">
+        <f t="array" ref="M237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N237" s="11" cm="1">
+        <f t="array" ref="N237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O237" s="11" cm="1">
+        <f t="array" ref="O237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P237" s="11" cm="1">
+        <f t="array" ref="P237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q237" s="11" cm="1">
+        <f t="array" ref="Q237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R237" s="11" cm="1">
+        <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S237" s="14" cm="1">
+        <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D238" s="1" t="str" cm="1">
+        <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E238" s="11" cm="1">
+        <f t="array" ref="E238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>16</v>
+      </c>
+      <c r="F238" s="11" cm="1">
+        <f t="array" ref="F238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.75</v>
+      </c>
+      <c r="G238" s="11" cm="1">
+        <f t="array" ref="G238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H238" s="11" cm="1">
+        <f t="array" ref="H238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I238" s="11" cm="1">
+        <f t="array" ref="I238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J238" s="11" cm="1">
+        <f t="array" ref="J238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K238" s="11" cm="1">
+        <f t="array" ref="K238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L238" s="11" cm="1">
+        <f t="array" ref="L238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M238" s="11" cm="1">
+        <f t="array" ref="M238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N238" s="11" cm="1">
+        <f t="array" ref="N238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O238" s="11" cm="1">
+        <f t="array" ref="O238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P238" s="11" cm="1">
+        <f t="array" ref="P238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q238" s="11" cm="1">
+        <f t="array" ref="Q238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R238" s="11" cm="1">
+        <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S238" s="14" cm="1">
+        <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D239" s="1" t="str" cm="1">
+        <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E239" s="11" cm="1">
+        <f t="array" ref="E239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>17</v>
+      </c>
+      <c r="F239" s="11" cm="1">
+        <f t="array" ref="F239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.76</v>
+      </c>
+      <c r="G239" s="11" cm="1">
+        <f t="array" ref="G239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H239" s="11" cm="1">
+        <f t="array" ref="H239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="I239" s="11" cm="1">
+        <f t="array" ref="I239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J239" s="11" cm="1">
+        <f t="array" ref="J239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K239" s="11" cm="1">
+        <f t="array" ref="K239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L239" s="11" cm="1">
+        <f t="array" ref="L239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M239" s="11" cm="1">
+        <f t="array" ref="M239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N239" s="11" cm="1">
+        <f t="array" ref="N239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O239" s="11" cm="1">
+        <f t="array" ref="O239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P239" s="11" cm="1">
+        <f t="array" ref="P239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q239" s="11" cm="1">
+        <f t="array" ref="Q239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R239" s="11" cm="1">
+        <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S239" s="14" cm="1">
+        <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D240" s="1" t="str" cm="1">
+        <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E240" s="11" cm="1">
+        <f t="array" ref="E240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>18</v>
+      </c>
+      <c r="F240" s="11" cm="1">
+        <f t="array" ref="F240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.77</v>
+      </c>
+      <c r="G240" s="11" cm="1">
+        <f t="array" ref="G240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H240" s="11" cm="1">
+        <f t="array" ref="H240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.22</v>
+      </c>
+      <c r="I240" s="11" cm="1">
+        <f t="array" ref="I240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J240" s="11" cm="1">
+        <f t="array" ref="J240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K240" s="11" cm="1">
+        <f t="array" ref="K240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L240" s="11" cm="1">
+        <f t="array" ref="L240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M240" s="11" cm="1">
+        <f t="array" ref="M240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N240" s="11" cm="1">
+        <f t="array" ref="N240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O240" s="11" cm="1">
+        <f t="array" ref="O240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P240" s="11" cm="1">
+        <f t="array" ref="P240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q240" s="11" cm="1">
+        <f t="array" ref="Q240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R240" s="11" cm="1">
+        <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S240" s="14" cm="1">
+        <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D241" s="1" t="str" cm="1">
+        <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E241" s="11" cm="1">
+        <f t="array" ref="E241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>19</v>
+      </c>
+      <c r="F241" s="11" cm="1">
+        <f t="array" ref="F241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.77</v>
+      </c>
+      <c r="G241" s="11" cm="1">
+        <f t="array" ref="G241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H241" s="11" cm="1">
+        <f t="array" ref="H241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.24</v>
+      </c>
+      <c r="I241" s="11" cm="1">
+        <f t="array" ref="I241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J241" s="11" cm="1">
+        <f t="array" ref="J241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K241" s="11" cm="1">
+        <f t="array" ref="K241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L241" s="11" cm="1">
+        <f t="array" ref="L241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M241" s="11" cm="1">
+        <f t="array" ref="M241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N241" s="11" cm="1">
+        <f t="array" ref="N241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O241" s="11" cm="1">
+        <f t="array" ref="O241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P241" s="11" cm="1">
+        <f t="array" ref="P241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q241" s="11" cm="1">
+        <f t="array" ref="Q241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R241" s="11" cm="1">
+        <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S241" s="14" cm="1">
+        <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D242" s="1" t="str" cm="1">
+        <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E242" s="11" cm="1">
+        <f t="array" ref="E242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>20</v>
+      </c>
+      <c r="F242" s="11" cm="1">
+        <f t="array" ref="F242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G242" s="11" cm="1">
+        <f t="array" ref="G242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H242" s="11" cm="1">
+        <f t="array" ref="H242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.26</v>
+      </c>
+      <c r="I242" s="11" cm="1">
+        <f t="array" ref="I242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J242" s="11" cm="1">
+        <f t="array" ref="J242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K242" s="11" cm="1">
+        <f t="array" ref="K242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L242" s="11" cm="1">
+        <f t="array" ref="L242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M242" s="11" cm="1">
+        <f t="array" ref="M242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N242" s="11" cm="1">
+        <f t="array" ref="N242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O242" s="11" cm="1">
+        <f t="array" ref="O242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P242" s="11" cm="1">
+        <f t="array" ref="P242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q242" s="11" cm="1">
+        <f t="array" ref="Q242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R242" s="11" cm="1">
+        <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S242" s="14" cm="1">
+        <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D243" s="1" t="str" cm="1">
+        <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E243" s="11" cm="1">
+        <f t="array" ref="E243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>21</v>
+      </c>
+      <c r="F243" s="11" cm="1">
+        <f t="array" ref="F243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G243" s="11" cm="1">
+        <f t="array" ref="G243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H243" s="11" cm="1">
+        <f t="array" ref="H243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I243" s="11" cm="1">
+        <f t="array" ref="I243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J243" s="11" cm="1">
+        <f t="array" ref="J243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K243" s="11" cm="1">
+        <f t="array" ref="K243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L243" s="11" cm="1">
+        <f t="array" ref="L243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M243" s="11" cm="1">
+        <f t="array" ref="M243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N243" s="11" cm="1">
+        <f t="array" ref="N243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O243" s="11" cm="1">
+        <f t="array" ref="O243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P243" s="11" cm="1">
+        <f t="array" ref="P243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q243" s="11" cm="1">
+        <f t="array" ref="Q243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R243" s="11" cm="1">
+        <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S243" s="14" cm="1">
+        <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D244" s="1" t="str" cm="1">
+        <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E244" s="11" cm="1">
+        <f t="array" ref="E244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>22</v>
+      </c>
+      <c r="F244" s="11" cm="1">
+        <f t="array" ref="F244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G244" s="11" cm="1">
+        <f t="array" ref="G244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H244" s="11" cm="1">
+        <f t="array" ref="H244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.31</v>
+      </c>
+      <c r="I244" s="11" cm="1">
+        <f t="array" ref="I244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J244" s="11" cm="1">
+        <f t="array" ref="J244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K244" s="11" cm="1">
+        <f t="array" ref="K244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L244" s="11" cm="1">
+        <f t="array" ref="L244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M244" s="11" cm="1">
+        <f t="array" ref="M244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N244" s="11" cm="1">
+        <f t="array" ref="N244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O244" s="11" cm="1">
+        <f t="array" ref="O244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P244" s="11" cm="1">
+        <f t="array" ref="P244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q244" s="11" cm="1">
+        <f t="array" ref="Q244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R244" s="11" cm="1">
+        <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S244" s="14" cm="1">
+        <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D245" s="1" t="str" cm="1">
+        <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E245" s="11" cm="1">
+        <f t="array" ref="E245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>23</v>
+      </c>
+      <c r="F245" s="11" cm="1">
+        <f t="array" ref="F245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G245" s="11" cm="1">
+        <f t="array" ref="G245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H245" s="11" cm="1">
+        <f t="array" ref="H245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.34</v>
+      </c>
+      <c r="I245" s="11" cm="1">
+        <f t="array" ref="I245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J245" s="11" cm="1">
+        <f t="array" ref="J245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K245" s="11" cm="1">
+        <f t="array" ref="K245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L245" s="11" cm="1">
+        <f t="array" ref="L245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M245" s="11" cm="1">
+        <f t="array" ref="M245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N245" s="11" cm="1">
+        <f t="array" ref="N245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O245" s="11" cm="1">
+        <f t="array" ref="O245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P245" s="11" cm="1">
+        <f t="array" ref="P245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q245" s="11" cm="1">
+        <f t="array" ref="Q245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R245" s="11" cm="1">
+        <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S245" s="14" cm="1">
+        <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D246" s="1" t="str" cm="1">
+        <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E246" s="11" cm="1">
+        <f t="array" ref="E246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>24</v>
+      </c>
+      <c r="F246" s="11" cm="1">
+        <f t="array" ref="F246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G246" s="11" cm="1">
+        <f t="array" ref="G246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H246" s="11" cm="1">
+        <f t="array" ref="H246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.37</v>
+      </c>
+      <c r="I246" s="11" cm="1">
+        <f t="array" ref="I246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J246" s="11" cm="1">
+        <f t="array" ref="J246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K246" s="11" cm="1">
+        <f t="array" ref="K246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L246" s="11" cm="1">
+        <f t="array" ref="L246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M246" s="11" cm="1">
+        <f t="array" ref="M246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N246" s="11" cm="1">
+        <f t="array" ref="N246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O246" s="11" cm="1">
+        <f t="array" ref="O246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P246" s="11" cm="1">
+        <f t="array" ref="P246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q246" s="11" cm="1">
+        <f t="array" ref="Q246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R246" s="11" cm="1">
+        <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S246" s="14" cm="1">
+        <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D247" s="1" t="str" cm="1">
+        <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E247" s="11" cm="1">
+        <f t="array" ref="E247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>25</v>
+      </c>
+      <c r="F247" s="11" cm="1">
+        <f t="array" ref="F247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G247" s="11" cm="1">
+        <f t="array" ref="G247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H247" s="11" cm="1">
+        <f t="array" ref="H247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.41</v>
+      </c>
+      <c r="I247" s="11" cm="1">
+        <f t="array" ref="I247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J247" s="11" cm="1">
+        <f t="array" ref="J247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K247" s="11" cm="1">
+        <f t="array" ref="K247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L247" s="11" cm="1">
+        <f t="array" ref="L247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M247" s="11" cm="1">
+        <f t="array" ref="M247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N247" s="11" cm="1">
+        <f t="array" ref="N247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O247" s="11" cm="1">
+        <f t="array" ref="O247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P247" s="11" cm="1">
+        <f t="array" ref="P247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q247" s="11" cm="1">
+        <f t="array" ref="Q247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R247" s="11" cm="1">
+        <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S247" s="14" cm="1">
+        <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D248" s="1" t="str" cm="1">
+        <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E248" s="11" cm="1">
+        <f t="array" ref="E248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>26</v>
+      </c>
+      <c r="F248" s="11" cm="1">
+        <f t="array" ref="F248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G248" s="11" cm="1">
+        <f t="array" ref="G248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H248" s="11" cm="1">
+        <f t="array" ref="H248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.44</v>
+      </c>
+      <c r="I248" s="11" cm="1">
+        <f t="array" ref="I248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J248" s="11" cm="1">
+        <f t="array" ref="J248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K248" s="11" cm="1">
+        <f t="array" ref="K248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L248" s="11" cm="1">
+        <f t="array" ref="L248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M248" s="11" cm="1">
+        <f t="array" ref="M248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N248" s="11" cm="1">
+        <f t="array" ref="N248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O248" s="11" cm="1">
+        <f t="array" ref="O248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P248" s="11" cm="1">
+        <f t="array" ref="P248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q248" s="11" cm="1">
+        <f t="array" ref="Q248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R248" s="11" cm="1">
+        <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S248" s="14" cm="1">
+        <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D249" s="1" t="str" cm="1">
+        <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E249" s="11" cm="1">
+        <f t="array" ref="E249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>27</v>
+      </c>
+      <c r="F249" s="11" cm="1">
+        <f t="array" ref="F249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G249" s="11" cm="1">
+        <f t="array" ref="G249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H249" s="11" cm="1">
+        <f t="array" ref="H249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.48</v>
+      </c>
+      <c r="I249" s="11" cm="1">
+        <f t="array" ref="I249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J249" s="11" cm="1">
+        <f t="array" ref="J249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K249" s="11" cm="1">
+        <f t="array" ref="K249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L249" s="11" cm="1">
+        <f t="array" ref="L249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M249" s="11" cm="1">
+        <f t="array" ref="M249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N249" s="11" cm="1">
+        <f t="array" ref="N249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O249" s="11" cm="1">
+        <f t="array" ref="O249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P249" s="11" cm="1">
+        <f t="array" ref="P249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q249" s="11" cm="1">
+        <f t="array" ref="Q249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R249" s="11" cm="1">
+        <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S249" s="14" cm="1">
+        <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D250" s="1" t="str" cm="1">
+        <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E250" s="11" t="str" cm="1">
+        <f t="array" ref="E250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>≥28</v>
+      </c>
+      <c r="F250" s="11" cm="1">
+        <f t="array" ref="F250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G250" s="11" cm="1">
+        <f t="array" ref="G250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H250" s="11" cm="1">
+        <f t="array" ref="H250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I250" s="11" cm="1">
+        <f t="array" ref="I250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J250" s="11" cm="1">
+        <f t="array" ref="J250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K250" s="11" cm="1">
+        <f t="array" ref="K250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L250" s="11" cm="1">
+        <f t="array" ref="L250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M250" s="11" cm="1">
+        <f t="array" ref="M250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N250" s="11" cm="1">
+        <f t="array" ref="N250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O250" s="11" cm="1">
+        <f t="array" ref="O250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P250" s="11" cm="1">
+        <f t="array" ref="P250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q250" s="11" cm="1">
+        <f t="array" ref="Q250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R250" s="11" cm="1">
+        <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S250" s="14" cm="1">
+        <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="15">
-    <tablePart r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="16">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -5044,6 +6879,8 @@
     <tablePart r:id="rId13"/>
     <tablePart r:id="rId14"/>
     <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5064,12 +6901,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5268,24 +7107,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5310,12 +7150,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Common_v02.xlsx
+++ b/Excel/Common_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6FEFB5-2EBA-45CB-AFD0-37A0943ACDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF39F33-F015-47E3-B46D-EB4BA39A554C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="105" windowWidth="28875" windowHeight="16890" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="16890" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="3" r:id="rId1"/>
@@ -37,6 +37,8 @@
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
     <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
@@ -48,6 +50,7 @@
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -984,7 +987,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -1021,10 +1024,7 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="54">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2901,7 +2901,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="825" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="849" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -5558,117 +5558,117 @@
       </c>
     </row>
     <row r="231" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D231" s="14" t="s">
+      <c r="D231" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E231" s="14" t="s">
+      <c r="E231" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F231" s="15" t="s">
+      <c r="F231" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G231" s="14" t="s">
+      <c r="G231" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H231" s="14" t="s">
+      <c r="H231" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I231" s="14" t="s">
+      <c r="I231" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J231" s="14" t="s">
+      <c r="J231" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K231" s="14" t="s">
+      <c r="K231" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L231" s="14" t="s">
+      <c r="L231" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M231" s="14" t="s">
+      <c r="M231" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N231" s="14" t="s">
+      <c r="N231" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="O231" s="14" t="s">
+      <c r="O231" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="P231" s="14" t="s">
+      <c r="P231" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="Q231" s="14" t="s">
+      <c r="Q231" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="R231" s="14" t="s">
+      <c r="R231" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="S231" s="14" t="s">
+      <c r="S231" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D232" s="14" t="str" cm="1">
+      <c r="D232" s="11" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E232" s="14" t="str" cm="1">
+      <c r="E232" s="11" t="str" cm="1">
         <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>≤10</v>
       </c>
-      <c r="F232" s="14" cm="1">
+      <c r="F232" s="11" cm="1">
         <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.66</v>
       </c>
-      <c r="G232" s="14" cm="1">
+      <c r="G232" s="11" cm="1">
         <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H232" s="14" cm="1">
+      <c r="H232" s="11" cm="1">
         <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="I232" s="14" cm="1">
+      <c r="I232" s="11" cm="1">
         <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J232" s="14" cm="1">
+      <c r="J232" s="11" cm="1">
         <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K232" s="14" cm="1">
+      <c r="K232" s="11" cm="1">
         <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L232" s="14" cm="1">
+      <c r="L232" s="11" cm="1">
         <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M232" s="14" cm="1">
+      <c r="M232" s="11" cm="1">
         <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N232" s="14" cm="1">
+      <c r="N232" s="11" cm="1">
         <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O232" s="14" cm="1">
+      <c r="O232" s="11" cm="1">
         <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P232" s="14" cm="1">
+      <c r="P232" s="11" cm="1">
         <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q232" s="14" cm="1">
+      <c r="Q232" s="11" cm="1">
         <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R232" s="14" cm="1">
+      <c r="R232" s="11" cm="1">
         <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S232" s="14" cm="1">
+      <c r="S232" s="11" cm="1">
         <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>10</v>
       </c>
@@ -5734,7 +5734,7 @@
         <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S233" s="14" cm="1">
+      <c r="S233" s="11" cm="1">
         <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>11</v>
       </c>
@@ -5800,7 +5800,7 @@
         <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S234" s="14" cm="1">
+      <c r="S234" s="11" cm="1">
         <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>12</v>
       </c>
@@ -5866,7 +5866,7 @@
         <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S235" s="14" cm="1">
+      <c r="S235" s="11" cm="1">
         <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>13</v>
       </c>
@@ -5932,7 +5932,7 @@
         <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S236" s="14" cm="1">
+      <c r="S236" s="11" cm="1">
         <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>14</v>
       </c>
@@ -5998,7 +5998,7 @@
         <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S237" s="14" cm="1">
+      <c r="S237" s="11" cm="1">
         <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>15</v>
       </c>
@@ -6064,7 +6064,7 @@
         <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S238" s="14" cm="1">
+      <c r="S238" s="11" cm="1">
         <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>16</v>
       </c>
@@ -6130,7 +6130,7 @@
         <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S239" s="14" cm="1">
+      <c r="S239" s="11" cm="1">
         <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>17</v>
       </c>
@@ -6196,7 +6196,7 @@
         <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S240" s="14" cm="1">
+      <c r="S240" s="11" cm="1">
         <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>18</v>
       </c>
@@ -6262,7 +6262,7 @@
         <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S241" s="14" cm="1">
+      <c r="S241" s="11" cm="1">
         <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>19</v>
       </c>
@@ -6328,7 +6328,7 @@
         <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S242" s="14" cm="1">
+      <c r="S242" s="11" cm="1">
         <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>20</v>
       </c>
@@ -6394,7 +6394,7 @@
         <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S243" s="14" cm="1">
+      <c r="S243" s="11" cm="1">
         <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>21</v>
       </c>
@@ -6460,7 +6460,7 @@
         <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S244" s="14" cm="1">
+      <c r="S244" s="11" cm="1">
         <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>22</v>
       </c>
@@ -6526,7 +6526,7 @@
         <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S245" s="14" cm="1">
+      <c r="S245" s="11" cm="1">
         <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>23</v>
       </c>
@@ -6592,7 +6592,7 @@
         <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S246" s="14" cm="1">
+      <c r="S246" s="11" cm="1">
         <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>24</v>
       </c>
@@ -6658,7 +6658,7 @@
         <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S247" s="14" cm="1">
+      <c r="S247" s="11" cm="1">
         <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>25</v>
       </c>
@@ -6724,7 +6724,7 @@
         <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S248" s="14" cm="1">
+      <c r="S248" s="11" cm="1">
         <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>26</v>
       </c>
@@ -6790,7 +6790,7 @@
         <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S249" s="14" cm="1">
+      <c r="S249" s="11" cm="1">
         <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>27</v>
       </c>
@@ -6856,7 +6856,7 @@
         <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S250" s="14" cm="1">
+      <c r="S250" s="11" cm="1">
         <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>28</v>
       </c>
@@ -6901,14 +6901,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7107,25 +7105,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7150,9 +7147,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Common_v02.xlsx
+++ b/Excel/Common_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF39F33-F015-47E3-B46D-EB4BA39A554C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480B05D6-AEA0-4B4C-B1A3-2ADE4CBF62B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="16890" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2970" yWindow="1590" windowWidth="28800" windowHeight="16890" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="3" r:id="rId1"/>
@@ -97,6 +97,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title">_xlfn.LAMBDA("Emission factor for organic fertiliser and crop residues returned to the soil")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
@@ -206,6 +213,7 @@
     <definedName name="Step3">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -263,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
   <si>
     <t>Climate zone</t>
   </si>
@@ -461,6 +469,12 @@
   </si>
   <si>
     <t>MAT raw</t>
+  </si>
+  <si>
+    <t>Climate Zone</t>
+  </si>
+  <si>
+    <t>EFNi &amp; EFN2Oi</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1001,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -1025,6 +1039,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1089,7 +1106,31 @@
     <cellStyle name="Unit no indent" xfId="53" xr:uid="{2829D020-DAD8-4B7D-9262-450720E27D2B}"/>
     <cellStyle name="Unit total" xfId="25" xr:uid="{65428923-3DAD-47B6-8DDF-0EBD05E7C55B}"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="48">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2132,20 +2173,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="46"/>
-      <tableStyleElement type="headerRow" dxfId="45"/>
-      <tableStyleElement type="totalRow" dxfId="44"/>
-      <tableStyleElement type="firstColumn" dxfId="43"/>
-      <tableStyleElement type="firstRowStripe" dxfId="42"/>
-      <tableStyleElement type="secondRowStripe" dxfId="41"/>
+      <tableStyleElement type="wholeTable" dxfId="47"/>
+      <tableStyleElement type="headerRow" dxfId="46"/>
+      <tableStyleElement type="totalRow" dxfId="45"/>
+      <tableStyleElement type="firstColumn" dxfId="44"/>
+      <tableStyleElement type="firstRowStripe" dxfId="43"/>
+      <tableStyleElement type="secondRowStripe" dxfId="42"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="40"/>
-      <tableStyleElement type="headerRow" dxfId="39"/>
-      <tableStyleElement type="totalRow" dxfId="38"/>
-      <tableStyleElement type="firstColumn" dxfId="37"/>
-      <tableStyleElement type="firstRowStripe" dxfId="36"/>
-      <tableStyleElement type="secondRowStripe" dxfId="35"/>
+      <tableStyleElement type="wholeTable" dxfId="41"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="totalRow" dxfId="39"/>
+      <tableStyleElement type="firstColumn" dxfId="38"/>
+      <tableStyleElement type="firstRowStripe" dxfId="37"/>
+      <tableStyleElement type="secondRowStripe" dxfId="36"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -2288,7 +2329,7 @@
     <tableColumn id="1" xr3:uid="{CA74DB79-CAE7-4EF8-BA48-96421E9E9373}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="18">
+    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2336,7 +2377,7 @@
     <tableColumn id="1" xr3:uid="{B18D772B-2FE9-457A-A200-8E17C55C340C}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2354,7 +2395,7 @@
     <tableColumn id="1" xr3:uid="{718360C9-DDF8-4B7B-B842-EE0D39ED743F}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{876E0F1A-E7CF-4E69-9C3F-6E0E84FF4B5D}" name="EFPRP" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{876E0F1A-E7CF-4E69-9C3F-6E0E84FF4B5D}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2372,7 +2413,7 @@
     <tableColumn id="1" xr3:uid="{7CBE043C-4D22-47C3-AE18-5E55E64542E1}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{10DA8C9D-4358-470A-AF6C-AE27470313DE}" name="Season" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{10DA8C9D-4358-470A-AF6C-AE27470313DE}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2404,50 +2445,68 @@
     <tableColumn id="1" xr3:uid="{8E03AF9F-C6DD-415E-A42C-F2360BC32F72}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{07B3EB32-B4EC-4553-A2E1-8AE19F5ED1B8}" name="MAT (ºC)" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{07B3EB32-B4EC-4553-A2E1-8AE19F5ED1B8}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D245CE73-83DF-4AB6-BE51-10D787832614}" name="Anaerobic lagoon" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{D245CE73-83DF-4AB6-BE51-10D787832614}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96977D75-8628-4103-9D52-F7049CB2572B}" name="Digester / covered lagoons" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{96977D75-8628-4103-9D52-F7049CB2572B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F64B281A-2EA4-4881-94F1-FEBD2B18C677}" name="Liquid systems" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{F64B281A-2EA4-4881-94F1-FEBD2B18C677}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8934BA44-DDF5-433B-A89F-5DB281BAB7B5}" name="Daily spread" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{8934BA44-DDF5-433B-A89F-5DB281BAB7B5}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{699EC0ED-651C-48B9-9F8F-73146B12DB72}" name="Composting (passive windrow)" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{699EC0ED-651C-48B9-9F8F-73146B12DB72}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6E240578-9A8B-47C9-A356-B69BB058D44B}" name="Solid storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{6E240578-9A8B-47C9-A356-B69BB058D44B}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{922DD34E-8EDF-42D6-BE68-8D30A5F4A8CF}" name="Pit storage" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{922DD34E-8EDF-42D6-BE68-8D30A5F4A8CF}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{730FA508-F44F-43A0-8A87-F28C2DB6D4D5}" name="Deep litter" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{730FA508-F44F-43A0-8A87-F28C2DB6D4D5}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8BD6E90D-D2CF-4733-8286-F67C28172389}" name="Poultry manure with bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8BD6E90D-D2CF-4733-8286-F67C28172389}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE74F5BC-4374-40FF-85F0-AE26E403B07E}" name="Poultry manure without bedding" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{EE74F5BC-4374-40FF-85F0-AE26E403B07E}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B53034D9-4966-41B7-BD99-44BBB861677D}" name="Direct processing" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{B53034D9-4966-41B7-BD99-44BBB861677D}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{59F06DF1-1149-43CE-9ADC-FD2C1D44B8D0}" name="Direct application" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{59F06DF1-1149-43CE-9ADC-FD2C1D44B8D0}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E8CF9642-D223-420C-B387-277C82D3BB2E}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{E8CF9642-D223-420C-B387-277C82D3BB2E}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0B403FCE-8D29-4E28-99ED-B0004709790F}" name="MAT raw" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{0B403FCE-8D29-4E28-99ED-B0004709790F}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{3C12381E-3675-4A77-B50C-CAF33F1781C7}" name="Climate Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{15B1FB4A-EB78-4095-8978-98D149B427BD}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2540,49 +2599,49 @@
     <tableColumn id="1" xr3:uid="{8938BBE8-7B92-48A9-872B-3320D21DB635}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2600,7 +2659,7 @@
     <tableColumn id="1" xr3:uid="{2FCD4A06-823B-4A3F-89D0-46C27A9E1AA9}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2901,7 +2960,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="849" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="502" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2948,7 +3007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83968956-F921-4291-AAEE-DE11952DD430}">
-  <dimension ref="A1:BY250"/>
+  <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
@@ -6861,10 +6920,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D253" s="5" t="str" cm="1">
+        <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
+        <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
+      </c>
+    </row>
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D254" s="4" t="str" cm="1">
+        <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
+        <v>VEERG 2026: Table A.2.1.4</v>
+      </c>
+    </row>
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D255" s="1" t="str" cm="1">
+        <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
+        <v>EFNi &amp; EFN2Oi</v>
+      </c>
+    </row>
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D256" s="12" t="str" cm="1">
+        <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D257" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E257" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D258" s="15" t="str" cm="1">
+        <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E258" s="15" cm="1">
+        <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D259" s="1" t="str" cm="1">
+        <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E259" s="11" cm="1">
+        <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="16">
+  <tableParts count="17">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -6881,6 +6992,7 @@
     <tablePart r:id="rId15"/>
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6901,12 +7013,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7105,24 +7219,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7147,12 +7262,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Common_v02.xlsx
+++ b/Excel/Common_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480B05D6-AEA0-4B4C-B1A3-2ADE4CBF62B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD6DD20-F011-445D-B09A-D8B6120FF91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="1590" windowWidth="28800" windowHeight="16890" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1260" yWindow="1125" windowWidth="37140" windowHeight="20475" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="3" r:id="rId1"/>
@@ -213,7 +213,6 @@
     <definedName name="Step3">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1001,7 +1000,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -1039,9 +1038,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4410,31 +4406,31 @@
       </c>
       <c r="T97" s="11"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="12" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="12" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="12" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="12" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="12" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="12" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="12"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="12"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="5" t="str" cm="1">
@@ -6945,19 +6941,19 @@
       </c>
     </row>
     <row r="257" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D257" s="15" t="s">
+      <c r="D257" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E257" s="15" t="s">
+      <c r="E257" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="258" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D258" s="15" t="str" cm="1">
+      <c r="D258" s="11" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E258" s="15" cm="1">
+      <c r="E258" s="11" cm="1">
         <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -7013,17 +7009,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -7218,7 +7203,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -7227,22 +7227,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC